--- a/resources/templates/standard/K2100-05.xlsx
+++ b/resources/templates/standard/K2100-05.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>장기재고 품질 열화 Check Sheet</t>
   </si>
@@ -803,12 +806,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -829,7 +834,7 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
@@ -866,7 +871,7 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
@@ -903,7 +908,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
@@ -917,7 +922,7 @@
     </row>
     <row r="4" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -954,11 +959,11 @@
     </row>
     <row r="5" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -971,7 +976,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -1069,7 +1074,7 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -1143,7 +1148,7 @@
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -1291,7 +1296,7 @@
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -1439,7 +1444,7 @@
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -1513,7 +1518,7 @@
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
@@ -1587,7 +1592,7 @@
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -1735,7 +1740,7 @@
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
@@ -1805,7 +1810,7 @@
     </row>
     <row r="28" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1850,7 +1855,7 @@
     </row>
     <row r="29" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -1887,12 +1892,12 @@
     </row>
     <row r="30" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
@@ -1904,7 +1909,7 @@
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O30" s="19"/>
       <c r="P30" s="19"/>
@@ -1916,12 +1921,12 @@
       <c r="V30" s="19"/>
       <c r="W30" s="19"/>
       <c r="X30" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y30" s="20"/>
       <c r="Z30" s="20"/>
       <c r="AA30" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB30" s="21"/>
       <c r="AC30" s="21"/>
@@ -1935,7 +1940,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -1947,7 +1952,7 @@
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
       <c r="N31" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -1974,7 +1979,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
@@ -2008,12 +2013,12 @@
     </row>
     <row r="33" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2021,7 +2026,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2058,7 +2063,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -2068,7 +2073,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
@@ -2078,7 +2083,7 @@
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA34" s="5"/>
       <c r="AB34" s="5"/>
@@ -2230,7 +2235,7 @@
     </row>
     <row r="39" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2241,7 +2246,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -2269,7 +2274,7 @@
     </row>
     <row r="40" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="27"/>
       <c r="C40" s="27"/>
@@ -2280,7 +2285,7 @@
       <c r="H40" s="27"/>
       <c r="I40" s="27"/>
       <c r="J40" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" s="28"/>
       <c r="L40" s="28"/>
@@ -2308,7 +2313,7 @@
     </row>
     <row r="41" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -2345,7 +2350,7 @@
     </row>
     <row r="42" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2356,7 +2361,7 @@
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K42" s="31"/>
       <c r="L42" s="31"/>
@@ -2376,19 +2381,19 @@
       <c r="Z42" s="32"/>
       <c r="AA42" s="32"/>
       <c r="AB42" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF42" s="3"/>
       <c r="AG42" s="3"/>
     </row>
     <row r="43" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2425,7 +2430,7 @@
     </row>
     <row r="44" ht="17.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
